--- a/2026/URIARTE 630/Julio/EXPENSAS-Julio.xlsx
+++ b/2026/URIARTE 630/Julio/EXPENSAS-Julio.xlsx
@@ -1,31 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\URIARTE 630\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\URIARTE 630\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5436C29A-31A2-4D1B-97D8-92B529F4FCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F507839-B6EF-452E-A919-868494FFF957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
     <sheet name="prorrateo " sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'detalle y gastos'!$A$1:$F$30</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'prorrateo '!$A$1:$M$122</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="73">
   <si>
     <t>UF</t>
   </si>
@@ -219,16 +224,10 @@
     <t>ARTICULOS DE LIMPIEZA</t>
   </si>
   <si>
-    <t>TSG - MONTO A ABONAR: $120.541,8  (YA SE HABIA PREVISIONADO $200.000) - RESTA: $79.458,2 - CON ESE RESTO SE ABONA ARBA $60.055,7 (CUOTA 1, 2 Y 3)</t>
-  </si>
-  <si>
     <t>GASTOS BANCARIOS</t>
   </si>
   <si>
     <t>Egreso de ARBA</t>
-  </si>
-  <si>
-    <t>Egreso de TSG</t>
   </si>
   <si>
     <t>Subidos en JUN10 2026</t>
@@ -435,7 +434,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="59">
+  <borders count="57">
     <border>
       <left/>
       <right/>
@@ -1103,35 +1102,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1249,7 +1226,6 @@
     <xf numFmtId="166" fontId="1" fillId="3" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1274,40 +1250,66 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1315,13 +1317,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1346,53 +1346,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="15" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1471,9 +1437,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1511,9 +1477,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1546,9 +1512,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1581,9 +1564,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1760,43 +1760,43 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:G57"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="40.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.5546875" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="16"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6" s="19"/>
       <c r="E6" s="19"/>
       <c r="F6" s="19"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>26</v>
       </c>
@@ -1804,13 +1804,13 @@
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
       <c r="E7" s="17" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F7" s="45" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -1818,12 +1818,12 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="18" t="s">
         <v>9</v>
       </c>
@@ -1835,13 +1835,14 @@
       </c>
       <c r="F11" s="107"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="94"/>
-      <c r="C12" s="150">
-        <v>182740</v>
+      <c r="B12" s="93"/>
+      <c r="C12" s="145">
+        <f>182740/2</f>
+        <v>91370</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="29" t="s">
@@ -1851,12 +1852,12 @@
         <v>-756372.65192400618</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="94"/>
-      <c r="C13" s="150">
+      <c r="B13" s="93"/>
+      <c r="C13" s="145">
         <v>5842.51</v>
       </c>
       <c r="D13" s="4"/>
@@ -1865,272 +1866,257 @@
       </c>
       <c r="F13" s="88">
         <f>'prorrateo '!F10</f>
-        <v>1051393.4988500001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+        <v>477237.04705339996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="94"/>
-      <c r="C14" s="149">
-        <v>161862.98000000001</v>
+      <c r="B14" s="93"/>
+      <c r="C14" s="100">
+        <v>162057</v>
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="87" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="98">
-        <f>-C24</f>
-        <v>-518112.36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F14" s="97">
+        <f>-C23</f>
+        <v>-362147.93000000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="94"/>
-      <c r="C15" s="149">
+      <c r="B15" s="93"/>
+      <c r="C15" s="100">
         <v>20319.84</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="99">
+      <c r="F15" s="98">
         <v>-222358.64</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="94"/>
-      <c r="C16" s="150">
-        <v>133600</v>
+      <c r="B16" s="93"/>
+      <c r="C16" s="145">
+        <v>79600</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="87" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="102">
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
         <v>66</v>
       </c>
-      <c r="F16" s="103">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="108" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" s="109"/>
-      <c r="C17" s="112">
-        <f>-200000+120541.8+60055.7</f>
-        <v>-19402.5</v>
-      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="105"/>
       <c r="D17" s="4"/>
       <c r="E17" s="87" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" s="103">
+        <v>44</v>
+      </c>
+      <c r="F17" s="102">
         <v>-140969.29999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="110"/>
-      <c r="B18" s="111"/>
-      <c r="C18" s="113"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="89"/>
-    </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="21" t="s">
+    <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="90">
-        <f>SUM(C12:C18)</f>
-        <v>484962.83</v>
-      </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="31" t="s">
+      <c r="B18" s="94"/>
+      <c r="C18" s="89">
+        <f>SUM(C12:C17)</f>
+        <v>359189.35000000003</v>
+      </c>
+      <c r="D18" s="10"/>
+      <c r="E18" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F18" s="32">
         <f>SUM(F12:F17)</f>
-        <v>-586419.45307400613</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="42" t="s">
+        <v>-1004611.4748706063</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="94"/>
-      <c r="C20" s="91"/>
+      <c r="B19" s="93"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="13"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="93"/>
+      <c r="C20" s="100">
+        <v>0</v>
+      </c>
       <c r="D20" s="4"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="94"/>
-      <c r="C21" s="101">
-        <v>30200</v>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="64" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" s="101"/>
+      <c r="C21" s="103">
+        <v>2958.58</v>
       </c>
       <c r="D21" s="4"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="64" t="s">
-        <v>65</v>
-      </c>
-      <c r="B22" s="102"/>
-      <c r="C22" s="104">
-        <f>5899.06/2</f>
-        <v>2949.53</v>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="22"/>
+      <c r="C22" s="38">
+        <f>SUM(C19:C21)</f>
+        <v>2958.58</v>
       </c>
       <c r="D22" s="4"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="38">
-        <f>SUM(C20:C22)</f>
-        <v>33149.53</v>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" s="26"/>
+      <c r="C23" s="67">
+        <f>+C22+C18</f>
+        <v>362147.93000000005</v>
       </c>
       <c r="D23" s="4"/>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="26"/>
-      <c r="C24" s="67">
-        <f>+C23+C19</f>
-        <v>518112.36</v>
-      </c>
-      <c r="D24" s="4"/>
-    </row>
-    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="36" t="s">
+    </row>
+    <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="B25" s="37"/>
-      <c r="C25" s="68"/>
-    </row>
-    <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="69">
+      <c r="B24" s="37"/>
+      <c r="C24" s="68"/>
+    </row>
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="69">
         <v>0</v>
       </c>
-      <c r="F26" s="5"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="33" t="s">
+      <c r="F25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="44">
-        <f>SUM(C26:C26)</f>
+      <c r="B26" s="34"/>
+      <c r="C26" s="44">
+        <f>SUM(C25:C25)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="69"/>
+      <c r="C27" s="69"/>
+      <c r="F27" s="5"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="96">
+        <f>C27+C23</f>
+        <v>362147.93000000005</v>
+      </c>
       <c r="F28" s="5"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C29" s="97">
-        <f>C28+C24</f>
-        <v>518112.36</v>
-      </c>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="33" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B30" s="34"/>
-      <c r="C30" s="44">
-        <f>+C24+C27</f>
-        <v>518112.36</v>
-      </c>
-      <c r="E30" s="10"/>
-    </row>
-    <row r="35" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D35" s="5"/>
-    </row>
-    <row r="36" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="B29" s="34"/>
+      <c r="C29" s="44">
+        <f>+C23+C26</f>
+        <v>362147.93000000005</v>
+      </c>
+      <c r="E29" s="10"/>
+    </row>
+    <row r="34" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D34" s="5"/>
+    </row>
+    <row r="35" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+    </row>
+    <row r="36" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
     </row>
-    <row r="37" spans="4:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-    </row>
-    <row r="38" spans="4:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D38" s="10"/>
     </row>
-    <row r="39" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D39" s="10"/>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="12"/>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="12"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="13"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="11"/>
       <c r="B51" s="11"/>
-      <c r="C51" s="13"/>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C51" s="11"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="11"/>
       <c r="B52" s="11"/>
       <c r="C52" s="11"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
       <c r="B53" s="11"/>
       <c r="C53" s="11"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
       <c r="B54" s="11"/>
       <c r="C54" s="11"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="11"/>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
       <c r="B56" s="11"/>
       <c r="C56" s="11"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="11"/>
       <c r="B57" s="11"/>
       <c r="C57" s="11"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:C18"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -2148,53 +2134,53 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T121"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" style="1" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="25.33203125" customWidth="1"/>
-    <col min="4" max="4" width="6.88671875" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.88671875" customWidth="1"/>
-    <col min="8" max="8" width="13.88671875" customWidth="1"/>
-    <col min="9" max="9" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.85546875" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="12" width="14.33203125" customWidth="1"/>
-    <col min="13" max="13" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" style="14"/>
+    <col min="11" max="12" width="14.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="131" t="str">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A1" s="138" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de JULIO</v>
       </c>
-      <c r="B1" s="132"/>
-      <c r="C1" s="132"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
       <c r="D1" s="74"/>
       <c r="E1" s="75" t="s">
         <v>25</v>
       </c>
       <c r="F1" s="74"/>
-      <c r="G1" s="126" t="s">
+      <c r="G1" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="128"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="129">
+      <c r="H1" s="134"/>
+      <c r="I1" s="134"/>
+      <c r="J1" s="135"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="136">
         <f>O1</f>
-        <v>388232.51500000001</v>
-      </c>
-      <c r="M1" s="130"/>
+        <v>362147.93000000005</v>
+      </c>
+      <c r="M1" s="137"/>
       <c r="O1" s="14">
-        <v>388232.51500000001</v>
+        <v>362147.93000000005</v>
       </c>
       <c r="P1" s="14"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="76" t="str">
         <f>'detalle y gastos'!F7</f>
         <v>Vto. 17/08</v>
@@ -2205,52 +2191,49 @@
       <c r="E2" s="40"/>
       <c r="F2" s="41"/>
       <c r="G2" s="40" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H2" s="41"/>
       <c r="I2" s="41"/>
       <c r="J2" s="66"/>
       <c r="K2" s="66"/>
-      <c r="L2" s="114">
-        <v>300000</v>
-      </c>
-      <c r="M2" s="115"/>
-      <c r="O2" s="14">
-        <v>-315745.03999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="145" t="s">
+      <c r="L2" s="141">
+        <v>0</v>
+      </c>
+      <c r="M2" s="142"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" s="119" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="143" t="s">
+      <c r="C3" s="117" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="143" t="s">
+      <c r="E3" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="143" t="s">
+      <c r="F3" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="143" t="s">
+      <c r="G3" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="143" t="s">
+      <c r="H3" s="117" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="147" t="s">
+      <c r="I3" s="121" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="147" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" s="143" t="s">
+      <c r="J3" s="121" t="s">
+        <v>68</v>
+      </c>
+      <c r="K3" s="117" t="s">
         <v>58</v>
       </c>
       <c r="L3" s="6" t="s">
@@ -2260,33 +2243,33 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="146"/>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="120"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="144"/>
+      <c r="C4" s="118"/>
       <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="144"/>
-      <c r="F4" s="144"/>
-      <c r="G4" s="144"/>
-      <c r="H4" s="144"/>
-      <c r="I4" s="148"/>
-      <c r="J4" s="148"/>
-      <c r="K4" s="144"/>
+      <c r="E4" s="118"/>
+      <c r="F4" s="118"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="118"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="118"/>
       <c r="L4" s="71" t="str">
         <f>A2</f>
         <v>Vto. 17/08</v>
       </c>
-      <c r="M4" s="105" t="str">
+      <c r="M4" s="104" t="str">
         <f>O4</f>
         <v>Vto 19/07</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="77">
         <v>1</v>
       </c>
@@ -2299,15 +2282,16 @@
       <c r="D5" s="43">
         <v>0.5</v>
       </c>
-      <c r="E5" s="100">
-        <v>119827.29045</v>
-      </c>
-      <c r="F5" s="101">
-        <v>120000</v>
+      <c r="E5" s="99">
+        <v>81356.118600000002</v>
+      </c>
+      <c r="F5" s="100">
+        <f>81530</f>
+        <v>81530</v>
       </c>
       <c r="G5" s="72">
         <f>E5-F5</f>
-        <v>-172.70954999999958</v>
+        <v>-173.88139999999839</v>
       </c>
       <c r="H5" s="73">
         <f>IF(G5&gt;0,G5*8.4%,0)</f>
@@ -2315,7 +2299,7 @@
       </c>
       <c r="I5" s="23">
         <f>L$1*B5</f>
-        <v>81528.828150000001</v>
+        <v>76051.065300000002</v>
       </c>
       <c r="J5" s="9">
         <f>J$2*D5</f>
@@ -2324,14 +2308,14 @@
       <c r="K5" s="9"/>
       <c r="L5" s="9">
         <f t="shared" ref="L5:L9" si="0">I5+J5+H5+G5+K5</f>
-        <v>81356.118600000002</v>
+        <v>75877.183900000004</v>
       </c>
       <c r="M5" s="79">
         <f>L5+L5*4%</f>
-        <v>84610.363343999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>78912.271256000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" s="77">
         <v>2</v>
       </c>
@@ -2344,39 +2328,39 @@
       <c r="D6" s="43">
         <v>0.5</v>
       </c>
-      <c r="E6" s="100">
-        <v>552140.78429836</v>
-      </c>
-      <c r="F6" s="101">
+      <c r="E6" s="99">
+        <v>708637.81257942226</v>
+      </c>
+      <c r="F6" s="100">
         <v>0</v>
       </c>
       <c r="G6" s="72">
         <f t="shared" ref="G6:G9" si="1">E6-F6</f>
-        <v>552140.78429836</v>
+        <v>708637.81257942226</v>
       </c>
       <c r="H6" s="73">
         <f t="shared" ref="H6:H9" si="2">IF(G6&gt;0,G6*8.4%,0)</f>
-        <v>46379.825881062243</v>
+        <v>59525.576256671477</v>
       </c>
       <c r="I6" s="23">
         <f>L$1*B6</f>
-        <v>62117.202400000002</v>
+        <v>57943.668800000007</v>
       </c>
       <c r="J6" s="9">
         <f>L$2*B6</f>
-        <v>48000</v>
+        <v>0</v>
       </c>
       <c r="K6" s="9"/>
       <c r="L6" s="9">
         <f t="shared" si="0"/>
-        <v>708637.81257942226</v>
+        <v>826107.0576360937</v>
       </c>
       <c r="M6" s="79">
         <f t="shared" ref="M6:M9" si="3">L6+L6*4%</f>
-        <v>736983.32508259919</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>859151.33994153747</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="77">
         <v>3</v>
       </c>
@@ -2387,40 +2371,40 @@
         <v>50</v>
       </c>
       <c r="D7" s="43"/>
-      <c r="E7" s="100">
-        <v>311194.99944044533</v>
-      </c>
-      <c r="F7" s="101">
-        <f>115370+181676</f>
-        <v>297046</v>
+      <c r="E7" s="99">
+        <v>159866.34354344275</v>
+      </c>
+      <c r="F7" s="100">
+        <f>94630</f>
+        <v>94630</v>
       </c>
       <c r="G7" s="72">
         <f t="shared" si="1"/>
-        <v>14148.999440445332</v>
+        <v>65236.343543442752</v>
       </c>
       <c r="H7" s="73">
         <f t="shared" si="2"/>
-        <v>1188.515952997408</v>
+        <v>5479.8528576491917</v>
       </c>
       <c r="I7" s="23">
         <f>L$1*B7</f>
-        <v>81528.828150000001</v>
+        <v>76051.065300000002</v>
       </c>
       <c r="J7" s="9">
         <f t="shared" ref="J7:J9" si="4">L$2*B7</f>
-        <v>63000</v>
-      </c>
-      <c r="K7" s="96"/>
+        <v>0</v>
+      </c>
+      <c r="K7" s="95"/>
       <c r="L7" s="9">
         <f>I7+J7+H7+G7+K7</f>
-        <v>159866.34354344275</v>
+        <v>146767.26170109195</v>
       </c>
       <c r="M7" s="79">
         <f t="shared" si="3"/>
-        <v>166260.99728518046</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>152637.95216913562</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="77">
         <v>4</v>
       </c>
@@ -2431,12 +2415,12 @@
         <v>45</v>
       </c>
       <c r="D8" s="43"/>
-      <c r="E8" s="100">
-        <v>186133.74884999997</v>
-      </c>
-      <c r="F8" s="101">
+      <c r="E8" s="99">
+        <v>144528.82815000002</v>
+      </c>
+      <c r="F8" s="100">
         <f>E8</f>
-        <v>186133.74884999997</v>
+        <v>144528.82815000002</v>
       </c>
       <c r="G8" s="72">
         <f t="shared" si="1"/>
@@ -2448,23 +2432,23 @@
       </c>
       <c r="I8" s="23">
         <f>L$1*B8</f>
-        <v>81528.828150000001</v>
+        <v>76051.065300000002</v>
       </c>
       <c r="J8" s="9">
         <f t="shared" si="4"/>
-        <v>63000</v>
+        <v>0</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9">
         <f t="shared" si="0"/>
-        <v>144528.82815000002</v>
+        <v>76051.065300000002</v>
       </c>
       <c r="M8" s="79">
         <f t="shared" si="3"/>
-        <v>150309.98127600001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>79093.107912000007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="77">
         <v>5</v>
       </c>
@@ -2475,40 +2459,40 @@
         <v>51</v>
       </c>
       <c r="D9" s="43"/>
-      <c r="E9" s="100">
-        <v>459301.74884999997</v>
-      </c>
-      <c r="F9" s="101">
-        <f>186133.75+262080</f>
-        <v>448213.75</v>
+      <c r="E9" s="99">
+        <v>156548.21890339997</v>
+      </c>
+      <c r="F9" s="100">
+        <f>E9</f>
+        <v>156548.21890339997</v>
       </c>
       <c r="G9" s="72">
         <f t="shared" si="1"/>
-        <v>11087.998849999974</v>
+        <v>0</v>
       </c>
       <c r="H9" s="73">
         <f t="shared" si="2"/>
-        <v>931.39190339999789</v>
+        <v>0</v>
       </c>
       <c r="I9" s="23">
         <f>L$1*B9</f>
-        <v>81528.828150000001</v>
+        <v>76051.065300000002</v>
       </c>
       <c r="J9" s="9">
         <f t="shared" si="4"/>
-        <v>63000</v>
+        <v>0</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9">
         <f t="shared" si="0"/>
-        <v>156548.21890339997</v>
+        <v>76051.065300000002</v>
       </c>
       <c r="M9" s="79">
         <f t="shared" si="3"/>
-        <v>162810.14765953599</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>79093.107912000007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="80" t="s">
         <v>7</v>
       </c>
@@ -2523,80 +2507,80 @@
       </c>
       <c r="E10" s="84">
         <f>SUM(E5:E9)</f>
-        <v>1628598.5718888054</v>
+        <v>1250937.321776265</v>
       </c>
       <c r="F10" s="84">
         <f>SUM(F5:F9)</f>
-        <v>1051393.4988500001</v>
+        <v>477237.04705339996</v>
       </c>
       <c r="G10" s="84">
         <f t="shared" si="5"/>
-        <v>551968.07474835997</v>
+        <v>708463.9311794223</v>
       </c>
       <c r="H10" s="84">
         <f t="shared" si="5"/>
-        <v>46379.825881062243</v>
+        <v>59525.576256671477</v>
       </c>
       <c r="I10" s="85">
         <f>SUM(I5:I9)</f>
-        <v>388232.51500000001</v>
+        <v>362147.93000000005</v>
       </c>
       <c r="J10" s="85">
         <f>SUM(J5:J9)</f>
-        <v>237000</v>
+        <v>0</v>
       </c>
       <c r="K10" s="85"/>
       <c r="L10" s="84">
         <f>SUM(L5:L9)</f>
-        <v>1250937.321776265</v>
+        <v>1200853.6338371853</v>
       </c>
       <c r="M10" s="86">
         <f>SUM(M5:M9)</f>
-        <v>1300974.8146473155</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="133"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="133"/>
-      <c r="E11" s="133"/>
-      <c r="F11" s="133"/>
-      <c r="G11" s="133"/>
-      <c r="H11" s="133"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="133"/>
-      <c r="K11" s="133"/>
-      <c r="L11" s="133"/>
-      <c r="M11" s="133"/>
-    </row>
-    <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1248887.7791906733</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="140"/>
+      <c r="B11" s="140"/>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="140"/>
+      <c r="L11" s="140"/>
+      <c r="M11" s="140"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C14" s="118" t="s">
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="119"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="119"/>
-      <c r="H14" s="119"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="128"/>
+      <c r="F14" s="128"/>
+      <c r="G14" s="128"/>
+      <c r="H14" s="128"/>
       <c r="I14" s="48"/>
       <c r="J14" s="49"/>
       <c r="K14" s="53"/>
       <c r="L14" s="53"/>
     </row>
-    <row r="15" spans="1:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C15" s="120" t="s">
+    <row r="15" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="119"/>
+      <c r="D15" s="128"/>
+      <c r="E15" s="128"/>
+      <c r="F15" s="128"/>
+      <c r="G15" s="128"/>
+      <c r="H15" s="128"/>
       <c r="I15" s="50"/>
       <c r="J15" s="51"/>
       <c r="K15" s="53"/>
@@ -2608,7 +2592,7 @@
         <v>96550</v>
       </c>
     </row>
-    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C16" s="48"/>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
@@ -2628,7 +2612,7 @@
         <v>27991.75</v>
       </c>
     </row>
-    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C17" s="50" t="s">
         <v>36</v>
       </c>
@@ -2650,7 +2634,7 @@
         <v>32000</v>
       </c>
     </row>
-    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C18" s="54"/>
       <c r="D18" s="55"/>
       <c r="E18" s="55"/>
@@ -2668,21 +2652,21 @@
         <v>24923.78</v>
       </c>
     </row>
-    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="116" t="s">
+    <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="130" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="117"/>
-      <c r="E19" s="117"/>
-      <c r="F19" s="117"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="117"/>
+      <c r="D19" s="131"/>
+      <c r="E19" s="131"/>
+      <c r="F19" s="131"/>
+      <c r="G19" s="131"/>
+      <c r="H19" s="131"/>
       <c r="I19" s="50"/>
       <c r="J19" s="51"/>
       <c r="K19" s="53"/>
       <c r="L19" s="53"/>
     </row>
-    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C20" s="50"/>
       <c r="D20" s="53"/>
       <c r="E20" s="53"/>
@@ -2700,7 +2684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C21" s="50" t="s">
         <v>38</v>
       </c>
@@ -2714,14 +2698,14 @@
         <v>39</v>
       </c>
       <c r="H21" s="56"/>
-      <c r="I21" s="121" t="s">
+      <c r="I21" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="122"/>
+      <c r="J21" s="126"/>
       <c r="K21" s="65"/>
       <c r="L21" s="65"/>
     </row>
-    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C22" s="50" t="s">
         <v>41</v>
       </c>
@@ -2740,19 +2724,19 @@
       <c r="K22" s="53"/>
       <c r="L22" s="53"/>
     </row>
-    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C23" s="50"/>
       <c r="D23" s="53"/>
       <c r="E23" s="53"/>
       <c r="F23" s="53"/>
       <c r="G23" s="53"/>
       <c r="H23" s="53"/>
-      <c r="I23" s="123"/>
-      <c r="J23" s="122"/>
+      <c r="I23" s="132"/>
+      <c r="J23" s="126"/>
       <c r="K23" s="65"/>
       <c r="L23" s="65"/>
     </row>
-    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C24" s="63" t="s">
         <v>44</v>
       </c>
@@ -2762,14 +2746,14 @@
       <c r="G24" s="53"/>
       <c r="H24" s="62">
         <f>L$1/5</f>
-        <v>77646.502999999997</v>
+        <v>72429.58600000001</v>
       </c>
       <c r="I24" s="50"/>
       <c r="J24" s="51"/>
       <c r="K24" s="53"/>
       <c r="L24" s="53"/>
     </row>
-    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C25" s="64" t="s">
         <v>29</v>
       </c>
@@ -2786,7 +2770,7 @@
       <c r="K25" s="53"/>
       <c r="L25" s="53"/>
     </row>
-    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C26" s="64" t="s">
         <v>27</v>
       </c>
@@ -2803,7 +2787,7 @@
       <c r="K26" s="53"/>
       <c r="L26" s="53"/>
     </row>
-    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C27" s="64" t="s">
         <v>30</v>
       </c>
@@ -2820,7 +2804,7 @@
       <c r="K27" s="53"/>
       <c r="L27" s="53"/>
     </row>
-    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="3:20" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="64" t="s">
         <v>28</v>
       </c>
@@ -2837,7 +2821,7 @@
       <c r="K28" s="53"/>
       <c r="L28" s="53"/>
     </row>
-    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="D29" s="53"/>
       <c r="E29" s="53"/>
       <c r="F29" s="53"/>
@@ -2848,7 +2832,7 @@
       <c r="K29" s="53"/>
       <c r="L29" s="53"/>
     </row>
-    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C30" s="64" t="s">
         <v>33</v>
       </c>
@@ -2865,7 +2849,7 @@
       <c r="K30" s="53"/>
       <c r="L30" s="53"/>
     </row>
-    <row r="31" spans="3:20" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
       <c r="C31" s="50"/>
       <c r="D31" s="53"/>
       <c r="E31" s="53"/>
@@ -2877,55 +2861,55 @@
       <c r="K31" s="53"/>
       <c r="L31" s="53"/>
     </row>
-    <row r="32" spans="3:20" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C32" s="124" t="s">
+    <row r="32" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="125"/>
-      <c r="E32" s="125"/>
-      <c r="F32" s="125"/>
-      <c r="G32" s="125"/>
-      <c r="H32" s="93">
+      <c r="D32" s="124"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="124"/>
+      <c r="G32" s="124"/>
+      <c r="H32" s="92">
         <f>SUM(H24:H31)</f>
-        <v>123012.8855</v>
+        <v>117795.96850000002</v>
       </c>
       <c r="I32" s="60"/>
       <c r="J32" s="61"/>
       <c r="K32" s="53"/>
       <c r="L32" s="53"/>
     </row>
-    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="35" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="36" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C36" s="118" t="s">
+    <row r="33" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="35" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="36" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="119"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="119"/>
-      <c r="G36" s="119"/>
-      <c r="H36" s="119"/>
+      <c r="D36" s="128"/>
+      <c r="E36" s="128"/>
+      <c r="F36" s="128"/>
+      <c r="G36" s="128"/>
+      <c r="H36" s="128"/>
       <c r="I36" s="48"/>
       <c r="J36" s="49"/>
       <c r="K36" s="53"/>
       <c r="L36" s="53"/>
     </row>
-    <row r="37" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C37" s="120" t="s">
+    <row r="37" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="119"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="119"/>
-      <c r="G37" s="119"/>
-      <c r="H37" s="119"/>
+      <c r="D37" s="128"/>
+      <c r="E37" s="128"/>
+      <c r="F37" s="128"/>
+      <c r="G37" s="128"/>
+      <c r="H37" s="128"/>
       <c r="I37" s="50"/>
       <c r="J37" s="51"/>
       <c r="K37" s="53"/>
       <c r="L37" s="53"/>
     </row>
-    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C38" s="48"/>
       <c r="D38" s="52"/>
       <c r="E38" s="52"/>
@@ -2939,7 +2923,7 @@
       <c r="K38" s="53"/>
       <c r="L38" s="53"/>
     </row>
-    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C39" s="50" t="s">
         <v>36</v>
       </c>
@@ -2956,7 +2940,7 @@
       <c r="K39" s="53"/>
       <c r="L39" s="53"/>
     </row>
-    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C40" s="54"/>
       <c r="D40" s="55"/>
       <c r="E40" s="55"/>
@@ -2968,21 +2952,21 @@
       <c r="K40" s="53"/>
       <c r="L40" s="53"/>
     </row>
-    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C41" s="116" t="s">
+    <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="130" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="117"/>
-      <c r="E41" s="117"/>
-      <c r="F41" s="117"/>
-      <c r="G41" s="117"/>
-      <c r="H41" s="117"/>
+      <c r="D41" s="131"/>
+      <c r="E41" s="131"/>
+      <c r="F41" s="131"/>
+      <c r="G41" s="131"/>
+      <c r="H41" s="131"/>
       <c r="I41" s="50"/>
       <c r="J41" s="51"/>
       <c r="K41" s="53"/>
       <c r="L41" s="53"/>
     </row>
-    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C42" s="50"/>
       <c r="D42" s="53"/>
       <c r="E42" s="53"/>
@@ -2994,7 +2978,7 @@
       <c r="K42" s="53"/>
       <c r="L42" s="53"/>
     </row>
-    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C43" s="50" t="s">
         <v>38</v>
       </c>
@@ -3008,14 +2992,14 @@
         <v>39</v>
       </c>
       <c r="H43" s="56"/>
-      <c r="I43" s="121" t="s">
+      <c r="I43" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="J43" s="122"/>
+      <c r="J43" s="126"/>
       <c r="K43" s="65"/>
       <c r="L43" s="65"/>
     </row>
-    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C44" s="50" t="s">
         <v>41</v>
       </c>
@@ -3034,19 +3018,19 @@
       <c r="K44" s="53"/>
       <c r="L44" s="53"/>
     </row>
-    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C45" s="50"/>
       <c r="D45" s="53"/>
       <c r="E45" s="53"/>
       <c r="F45" s="53"/>
       <c r="G45" s="53"/>
       <c r="H45" s="53"/>
-      <c r="I45" s="123"/>
-      <c r="J45" s="122"/>
+      <c r="I45" s="132"/>
+      <c r="J45" s="126"/>
       <c r="K45" s="65"/>
       <c r="L45" s="65"/>
     </row>
-    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C46" s="50" t="s">
         <v>44</v>
       </c>
@@ -3056,14 +3040,14 @@
       <c r="G46" s="53"/>
       <c r="H46" s="62">
         <f>L$1/5</f>
-        <v>77646.502999999997</v>
+        <v>72429.58600000001</v>
       </c>
       <c r="I46" s="50"/>
       <c r="J46" s="51"/>
       <c r="K46" s="53"/>
       <c r="L46" s="53"/>
     </row>
-    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C47" s="50"/>
       <c r="D47" s="53"/>
       <c r="E47" s="53"/>
@@ -3075,7 +3059,7 @@
       <c r="K47" s="53"/>
       <c r="L47" s="53"/>
     </row>
-    <row r="48" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C48" s="50"/>
       <c r="D48" s="53"/>
       <c r="E48" s="53"/>
@@ -3087,54 +3071,54 @@
       <c r="K48" s="53"/>
       <c r="L48" s="53"/>
     </row>
-    <row r="49" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C49" s="124" t="s">
+    <row r="49" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="D49" s="125"/>
-      <c r="E49" s="125"/>
-      <c r="F49" s="125"/>
-      <c r="G49" s="125"/>
-      <c r="H49" s="93">
+      <c r="D49" s="124"/>
+      <c r="E49" s="124"/>
+      <c r="F49" s="124"/>
+      <c r="G49" s="124"/>
+      <c r="H49" s="92">
         <f>M6</f>
-        <v>736983.32508259919</v>
+        <v>859151.33994153747</v>
       </c>
       <c r="I49" s="60"/>
       <c r="J49" s="61"/>
       <c r="K49" s="53"/>
       <c r="L49" s="53"/>
     </row>
-    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="52" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C52" s="118" t="s">
+    <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="D52" s="119"/>
-      <c r="E52" s="119"/>
-      <c r="F52" s="119"/>
-      <c r="G52" s="119"/>
-      <c r="H52" s="119"/>
+      <c r="D52" s="128"/>
+      <c r="E52" s="128"/>
+      <c r="F52" s="128"/>
+      <c r="G52" s="128"/>
+      <c r="H52" s="128"/>
       <c r="I52" s="48"/>
       <c r="J52" s="49"/>
       <c r="K52" s="53"/>
       <c r="L52" s="53"/>
     </row>
-    <row r="53" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C53" s="120" t="s">
+    <row r="53" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="D53" s="119"/>
-      <c r="E53" s="119"/>
-      <c r="F53" s="119"/>
-      <c r="G53" s="119"/>
-      <c r="H53" s="119"/>
+      <c r="D53" s="128"/>
+      <c r="E53" s="128"/>
+      <c r="F53" s="128"/>
+      <c r="G53" s="128"/>
+      <c r="H53" s="128"/>
       <c r="I53" s="50"/>
       <c r="J53" s="51"/>
       <c r="K53" s="53"/>
       <c r="L53" s="53"/>
     </row>
-    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C54" s="48"/>
       <c r="D54" s="52"/>
       <c r="E54" s="52"/>
@@ -3148,7 +3132,7 @@
       <c r="K54" s="53"/>
       <c r="L54" s="53"/>
     </row>
-    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C55" s="50" t="s">
         <v>36</v>
       </c>
@@ -3165,7 +3149,7 @@
       <c r="K55" s="53"/>
       <c r="L55" s="53"/>
     </row>
-    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C56" s="54"/>
       <c r="D56" s="55"/>
       <c r="E56" s="55"/>
@@ -3177,21 +3161,21 @@
       <c r="K56" s="53"/>
       <c r="L56" s="53"/>
     </row>
-    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C57" s="116" t="s">
+    <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C57" s="130" t="s">
         <v>37</v>
       </c>
-      <c r="D57" s="117"/>
-      <c r="E57" s="117"/>
-      <c r="F57" s="117"/>
-      <c r="G57" s="117"/>
-      <c r="H57" s="117"/>
+      <c r="D57" s="131"/>
+      <c r="E57" s="131"/>
+      <c r="F57" s="131"/>
+      <c r="G57" s="131"/>
+      <c r="H57" s="131"/>
       <c r="I57" s="50"/>
       <c r="J57" s="51"/>
       <c r="K57" s="53"/>
       <c r="L57" s="53"/>
     </row>
-    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C58" s="50"/>
       <c r="D58" s="53"/>
       <c r="E58" s="53"/>
@@ -3203,7 +3187,7 @@
       <c r="K58" s="53"/>
       <c r="L58" s="53"/>
     </row>
-    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C59" s="50" t="s">
         <v>38</v>
       </c>
@@ -3217,14 +3201,14 @@
         <v>39</v>
       </c>
       <c r="H59" s="56"/>
-      <c r="I59" s="121" t="s">
+      <c r="I59" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="J59" s="122"/>
+      <c r="J59" s="126"/>
       <c r="K59" s="65"/>
       <c r="L59" s="65"/>
     </row>
-    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C60" s="50" t="s">
         <v>41</v>
       </c>
@@ -3243,19 +3227,19 @@
       <c r="K60" s="53"/>
       <c r="L60" s="53"/>
     </row>
-    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C61" s="50"/>
       <c r="D61" s="53"/>
       <c r="E61" s="53"/>
       <c r="F61" s="53"/>
       <c r="G61" s="53"/>
       <c r="H61" s="53"/>
-      <c r="I61" s="123"/>
-      <c r="J61" s="122"/>
+      <c r="I61" s="132"/>
+      <c r="J61" s="126"/>
       <c r="K61" s="65"/>
       <c r="L61" s="65"/>
     </row>
-    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C62" s="50" t="s">
         <v>44</v>
       </c>
@@ -3265,14 +3249,14 @@
       <c r="G62" s="53"/>
       <c r="H62" s="62">
         <f>L$1/5</f>
-        <v>77646.502999999997</v>
+        <v>72429.58600000001</v>
       </c>
       <c r="I62" s="50"/>
       <c r="J62" s="51"/>
       <c r="K62" s="53"/>
       <c r="L62" s="53"/>
     </row>
-    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C63" s="64" t="s">
         <v>29</v>
       </c>
@@ -3289,7 +3273,7 @@
       <c r="K63" s="53"/>
       <c r="L63" s="53"/>
     </row>
-    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C64" s="64" t="s">
         <v>27</v>
       </c>
@@ -3306,7 +3290,7 @@
       <c r="K64" s="53"/>
       <c r="L64" s="53"/>
     </row>
-    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C65" s="64" t="s">
         <v>30</v>
       </c>
@@ -3323,7 +3307,7 @@
       <c r="K65" s="53"/>
       <c r="L65" s="53"/>
     </row>
-    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C66" s="64" t="s">
         <v>28</v>
       </c>
@@ -3340,7 +3324,7 @@
       <c r="K66" s="53"/>
       <c r="L66" s="53"/>
     </row>
-    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="D67" s="53"/>
       <c r="E67" s="53"/>
       <c r="F67" s="53"/>
@@ -3351,7 +3335,7 @@
       <c r="K67" s="53"/>
       <c r="L67" s="53"/>
     </row>
-    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="3:12" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C68" s="64" t="s">
         <v>33</v>
       </c>
@@ -3368,7 +3352,7 @@
       <c r="K68" s="53"/>
       <c r="L68" s="53"/>
     </row>
-    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="3:12" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="50"/>
       <c r="D69" s="53"/>
       <c r="E69" s="53"/>
@@ -3380,7 +3364,7 @@
       <c r="K69" s="53"/>
       <c r="L69" s="53"/>
     </row>
-    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C70" s="50"/>
       <c r="D70" s="53"/>
       <c r="E70" s="53"/>
@@ -3392,7 +3376,7 @@
       <c r="K70" s="53"/>
       <c r="L70" s="53"/>
     </row>
-    <row r="71" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C71" s="50"/>
       <c r="D71" s="53"/>
       <c r="E71" s="53"/>
@@ -3404,55 +3388,55 @@
       <c r="K71" s="53"/>
       <c r="L71" s="53"/>
     </row>
-    <row r="72" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C72" s="124" t="s">
+    <row r="72" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C72" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="D72" s="125"/>
-      <c r="E72" s="125"/>
-      <c r="F72" s="125"/>
-      <c r="G72" s="125"/>
-      <c r="H72" s="93">
+      <c r="D72" s="124"/>
+      <c r="E72" s="124"/>
+      <c r="F72" s="124"/>
+      <c r="G72" s="124"/>
+      <c r="H72" s="92">
         <f>SUM(H62:H71)</f>
-        <v>123012.8855</v>
+        <v>117795.96850000002</v>
       </c>
       <c r="I72" s="60"/>
       <c r="J72" s="61"/>
       <c r="K72" s="53"/>
       <c r="L72" s="53"/>
     </row>
-    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="76" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C76" s="118" t="s">
+    <row r="73" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C76" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="D76" s="119"/>
-      <c r="E76" s="119"/>
-      <c r="F76" s="119"/>
-      <c r="G76" s="119"/>
-      <c r="H76" s="119"/>
+      <c r="D76" s="128"/>
+      <c r="E76" s="128"/>
+      <c r="F76" s="128"/>
+      <c r="G76" s="128"/>
+      <c r="H76" s="128"/>
       <c r="I76" s="48"/>
       <c r="J76" s="49"/>
       <c r="K76" s="53"/>
       <c r="L76" s="53"/>
     </row>
-    <row r="77" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C77" s="120" t="s">
+    <row r="77" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C77" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="D77" s="119"/>
-      <c r="E77" s="119"/>
-      <c r="F77" s="119"/>
-      <c r="G77" s="119"/>
-      <c r="H77" s="119"/>
+      <c r="D77" s="128"/>
+      <c r="E77" s="128"/>
+      <c r="F77" s="128"/>
+      <c r="G77" s="128"/>
+      <c r="H77" s="128"/>
       <c r="I77" s="50"/>
       <c r="J77" s="51"/>
       <c r="K77" s="53"/>
       <c r="L77" s="53"/>
     </row>
-    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C78" s="48"/>
       <c r="D78" s="52"/>
       <c r="E78" s="52"/>
@@ -3466,7 +3450,7 @@
       <c r="K78" s="53"/>
       <c r="L78" s="53"/>
     </row>
-    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C79" s="50" t="s">
         <v>36</v>
       </c>
@@ -3483,7 +3467,7 @@
       <c r="K79" s="53"/>
       <c r="L79" s="53"/>
     </row>
-    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C80" s="54"/>
       <c r="D80" s="55"/>
       <c r="E80" s="55"/>
@@ -3495,21 +3479,21 @@
       <c r="K80" s="53"/>
       <c r="L80" s="53"/>
     </row>
-    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C81" s="116" t="s">
+    <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C81" s="130" t="s">
         <v>37</v>
       </c>
-      <c r="D81" s="117"/>
-      <c r="E81" s="117"/>
-      <c r="F81" s="117"/>
-      <c r="G81" s="117"/>
-      <c r="H81" s="117"/>
+      <c r="D81" s="131"/>
+      <c r="E81" s="131"/>
+      <c r="F81" s="131"/>
+      <c r="G81" s="131"/>
+      <c r="H81" s="131"/>
       <c r="I81" s="50"/>
       <c r="J81" s="51"/>
       <c r="K81" s="53"/>
       <c r="L81" s="53"/>
     </row>
-    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C82" s="50"/>
       <c r="D82" s="53"/>
       <c r="E82" s="53"/>
@@ -3521,7 +3505,7 @@
       <c r="K82" s="53"/>
       <c r="L82" s="53"/>
     </row>
-    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C83" s="50" t="s">
         <v>38</v>
       </c>
@@ -3535,14 +3519,14 @@
         <v>39</v>
       </c>
       <c r="H83" s="56"/>
-      <c r="I83" s="121" t="s">
+      <c r="I83" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="J83" s="122"/>
+      <c r="J83" s="126"/>
       <c r="K83" s="65"/>
       <c r="L83" s="65"/>
     </row>
-    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C84" s="50" t="s">
         <v>41</v>
       </c>
@@ -3561,19 +3545,19 @@
       <c r="K84" s="53"/>
       <c r="L84" s="53"/>
     </row>
-    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C85" s="50"/>
       <c r="D85" s="53"/>
       <c r="E85" s="53"/>
       <c r="F85" s="53"/>
       <c r="G85" s="53"/>
       <c r="H85" s="53"/>
-      <c r="I85" s="123"/>
-      <c r="J85" s="122"/>
+      <c r="I85" s="132"/>
+      <c r="J85" s="126"/>
       <c r="K85" s="65"/>
       <c r="L85" s="65"/>
     </row>
-    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C86" s="50" t="s">
         <v>44</v>
       </c>
@@ -3583,14 +3567,14 @@
       <c r="G86" s="53"/>
       <c r="H86" s="62">
         <f>L$1/5</f>
-        <v>77646.502999999997</v>
+        <v>72429.58600000001</v>
       </c>
       <c r="I86" s="50"/>
       <c r="J86" s="51"/>
       <c r="K86" s="53"/>
       <c r="L86" s="53"/>
     </row>
-    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C87" s="64" t="s">
         <v>29</v>
       </c>
@@ -3607,7 +3591,7 @@
       <c r="K87" s="53"/>
       <c r="L87" s="53"/>
     </row>
-    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C88" s="64" t="s">
         <v>27</v>
       </c>
@@ -3624,7 +3608,7 @@
       <c r="K88" s="53"/>
       <c r="L88" s="53"/>
     </row>
-    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C89" s="64" t="s">
         <v>30</v>
       </c>
@@ -3641,7 +3625,7 @@
       <c r="K89" s="53"/>
       <c r="L89" s="53"/>
     </row>
-    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="3:12" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="64" t="s">
         <v>28</v>
       </c>
@@ -3658,7 +3642,7 @@
       <c r="K90" s="53"/>
       <c r="L90" s="53"/>
     </row>
-    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="D91" s="53"/>
       <c r="E91" s="53"/>
       <c r="F91" s="53"/>
@@ -3669,7 +3653,7 @@
       <c r="K91" s="53"/>
       <c r="L91" s="53"/>
     </row>
-    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C92" s="64" t="s">
         <v>33</v>
       </c>
@@ -3686,7 +3670,7 @@
       <c r="K92" s="53"/>
       <c r="L92" s="53"/>
     </row>
-    <row r="93" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="D93" s="53"/>
       <c r="E93" s="53"/>
       <c r="F93" s="53"/>
@@ -3697,55 +3681,55 @@
       <c r="K93" s="53"/>
       <c r="L93" s="53"/>
     </row>
-    <row r="94" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C94" s="124" t="s">
+    <row r="94" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C94" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="D94" s="125"/>
-      <c r="E94" s="125"/>
-      <c r="F94" s="125"/>
-      <c r="G94" s="125"/>
-      <c r="H94" s="93">
+      <c r="D94" s="124"/>
+      <c r="E94" s="124"/>
+      <c r="F94" s="124"/>
+      <c r="G94" s="124"/>
+      <c r="H94" s="92">
         <f>SUM(H86:H93)</f>
-        <v>123012.8855</v>
+        <v>117795.96850000002</v>
       </c>
       <c r="I94" s="60"/>
       <c r="J94" s="61"/>
       <c r="K94" s="53"/>
       <c r="L94" s="53"/>
     </row>
-    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="97" spans="3:12" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="98" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C98" s="118" t="s">
+    <row r="95" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="97" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="98" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C98" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="D98" s="119"/>
-      <c r="E98" s="119"/>
-      <c r="F98" s="119"/>
-      <c r="G98" s="119"/>
-      <c r="H98" s="119"/>
+      <c r="D98" s="128"/>
+      <c r="E98" s="128"/>
+      <c r="F98" s="128"/>
+      <c r="G98" s="128"/>
+      <c r="H98" s="128"/>
       <c r="I98" s="48"/>
       <c r="J98" s="49"/>
       <c r="K98" s="53"/>
       <c r="L98" s="53"/>
     </row>
-    <row r="99" spans="3:12" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C99" s="120" t="s">
+    <row r="99" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C99" s="129" t="s">
         <v>35</v>
       </c>
-      <c r="D99" s="119"/>
-      <c r="E99" s="119"/>
-      <c r="F99" s="119"/>
-      <c r="G99" s="119"/>
-      <c r="H99" s="119"/>
+      <c r="D99" s="128"/>
+      <c r="E99" s="128"/>
+      <c r="F99" s="128"/>
+      <c r="G99" s="128"/>
+      <c r="H99" s="128"/>
       <c r="I99" s="50"/>
       <c r="J99" s="51"/>
       <c r="K99" s="53"/>
       <c r="L99" s="53"/>
     </row>
-    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C100" s="48"/>
       <c r="D100" s="52"/>
       <c r="E100" s="52"/>
@@ -3759,7 +3743,7 @@
       <c r="K100" s="53"/>
       <c r="L100" s="53"/>
     </row>
-    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C101" s="50" t="s">
         <v>36</v>
       </c>
@@ -3776,7 +3760,7 @@
       <c r="K101" s="53"/>
       <c r="L101" s="53"/>
     </row>
-    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C102" s="54"/>
       <c r="D102" s="55"/>
       <c r="E102" s="55"/>
@@ -3788,21 +3772,21 @@
       <c r="K102" s="53"/>
       <c r="L102" s="53"/>
     </row>
-    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="C103" s="116" t="s">
+    <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
+      <c r="C103" s="130" t="s">
         <v>37</v>
       </c>
-      <c r="D103" s="117"/>
-      <c r="E103" s="117"/>
-      <c r="F103" s="117"/>
-      <c r="G103" s="117"/>
-      <c r="H103" s="117"/>
+      <c r="D103" s="131"/>
+      <c r="E103" s="131"/>
+      <c r="F103" s="131"/>
+      <c r="G103" s="131"/>
+      <c r="H103" s="131"/>
       <c r="I103" s="50"/>
       <c r="J103" s="51"/>
       <c r="K103" s="53"/>
       <c r="L103" s="53"/>
     </row>
-    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C104" s="50"/>
       <c r="D104" s="53"/>
       <c r="E104" s="53"/>
@@ -3814,7 +3798,7 @@
       <c r="K104" s="53"/>
       <c r="L104" s="53"/>
     </row>
-    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C105" s="50" t="s">
         <v>38</v>
       </c>
@@ -3828,14 +3812,14 @@
         <v>39</v>
       </c>
       <c r="H105" s="56"/>
-      <c r="I105" s="121" t="s">
+      <c r="I105" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="J105" s="122"/>
+      <c r="J105" s="126"/>
       <c r="K105" s="65"/>
       <c r="L105" s="65"/>
     </row>
-    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C106" s="50" t="s">
         <v>41</v>
       </c>
@@ -3853,19 +3837,19 @@
       <c r="K106" s="53"/>
       <c r="L106" s="53"/>
     </row>
-    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C107" s="50"/>
       <c r="D107" s="53"/>
       <c r="E107" s="53"/>
       <c r="F107" s="53"/>
       <c r="G107" s="53"/>
       <c r="H107" s="53"/>
-      <c r="I107" s="123"/>
-      <c r="J107" s="122"/>
+      <c r="I107" s="132"/>
+      <c r="J107" s="126"/>
       <c r="K107" s="65"/>
       <c r="L107" s="65"/>
     </row>
-    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C108" s="50" t="s">
         <v>44</v>
       </c>
@@ -3875,14 +3859,14 @@
       <c r="G108" s="53"/>
       <c r="H108" s="62">
         <f>L$1/5</f>
-        <v>77646.502999999997</v>
+        <v>72429.58600000001</v>
       </c>
       <c r="I108" s="50"/>
       <c r="J108" s="51"/>
       <c r="K108" s="53"/>
       <c r="L108" s="53"/>
     </row>
-    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C109" s="64" t="s">
         <v>29</v>
       </c>
@@ -3899,7 +3883,7 @@
       <c r="K109" s="53"/>
       <c r="L109" s="53"/>
     </row>
-    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C110" s="64" t="s">
         <v>27</v>
       </c>
@@ -3916,7 +3900,7 @@
       <c r="K110" s="53"/>
       <c r="L110" s="53"/>
     </row>
-    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C111" s="64" t="s">
         <v>30</v>
       </c>
@@ -3933,7 +3917,7 @@
       <c r="K111" s="53"/>
       <c r="L111" s="53"/>
     </row>
-    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="C112" s="64" t="s">
         <v>28</v>
       </c>
@@ -3950,7 +3934,7 @@
       <c r="K112" s="53"/>
       <c r="L112" s="53"/>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="D113" s="53"/>
       <c r="E113" s="53"/>
       <c r="F113" s="53"/>
@@ -3961,7 +3945,7 @@
       <c r="K113" s="53"/>
       <c r="L113" s="53"/>
     </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="C114" s="64" t="s">
         <v>33</v>
       </c>
@@ -3978,7 +3962,7 @@
       <c r="K114" s="53"/>
       <c r="L114" s="53"/>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="D115" s="53"/>
       <c r="E115" s="53"/>
       <c r="F115" s="53"/>
@@ -3989,74 +3973,103 @@
       <c r="K115" s="53"/>
       <c r="L115" s="53"/>
     </row>
-    <row r="116" spans="1:13" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C116" s="124" t="s">
+    <row r="116" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C116" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="D116" s="125"/>
-      <c r="E116" s="125"/>
-      <c r="F116" s="125"/>
-      <c r="G116" s="125"/>
-      <c r="H116" s="93">
+      <c r="D116" s="124"/>
+      <c r="E116" s="124"/>
+      <c r="F116" s="124"/>
+      <c r="G116" s="124"/>
+      <c r="H116" s="92">
         <f>SUM(H108:H115)</f>
-        <v>123012.8855</v>
+        <v>117795.96850000002</v>
       </c>
       <c r="I116" s="60"/>
       <c r="J116" s="61"/>
       <c r="K116" s="53"/>
       <c r="L116" s="53"/>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="134" t="s">
-        <v>71</v>
-      </c>
-      <c r="B119" s="135"/>
-      <c r="C119" s="135"/>
-      <c r="D119" s="135"/>
-      <c r="E119" s="135"/>
-      <c r="F119" s="135"/>
-      <c r="G119" s="135"/>
-      <c r="H119" s="135"/>
-      <c r="I119" s="135"/>
-      <c r="J119" s="135"/>
-      <c r="K119" s="135"/>
-      <c r="L119" s="135"/>
-      <c r="M119" s="136"/>
-    </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A120" s="137"/>
-      <c r="B120" s="138"/>
-      <c r="C120" s="138"/>
-      <c r="D120" s="138"/>
-      <c r="E120" s="138"/>
-      <c r="F120" s="138"/>
-      <c r="G120" s="138"/>
-      <c r="H120" s="138"/>
-      <c r="I120" s="138"/>
-      <c r="J120" s="138"/>
-      <c r="K120" s="138"/>
-      <c r="L120" s="138"/>
-      <c r="M120" s="139"/>
-    </row>
-    <row r="121" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="140"/>
-      <c r="B121" s="141"/>
-      <c r="C121" s="141"/>
-      <c r="D121" s="141"/>
-      <c r="E121" s="141"/>
-      <c r="F121" s="141"/>
-      <c r="G121" s="141"/>
-      <c r="H121" s="141"/>
-      <c r="I121" s="141"/>
-      <c r="J121" s="141"/>
-      <c r="K121" s="141"/>
-      <c r="L121" s="141"/>
-      <c r="M121" s="142"/>
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="108" t="s">
+        <v>69</v>
+      </c>
+      <c r="B119" s="109"/>
+      <c r="C119" s="109"/>
+      <c r="D119" s="109"/>
+      <c r="E119" s="109"/>
+      <c r="F119" s="109"/>
+      <c r="G119" s="109"/>
+      <c r="H119" s="109"/>
+      <c r="I119" s="109"/>
+      <c r="J119" s="109"/>
+      <c r="K119" s="109"/>
+      <c r="L119" s="109"/>
+      <c r="M119" s="110"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="111"/>
+      <c r="B120" s="112"/>
+      <c r="C120" s="112"/>
+      <c r="D120" s="112"/>
+      <c r="E120" s="112"/>
+      <c r="F120" s="112"/>
+      <c r="G120" s="112"/>
+      <c r="H120" s="112"/>
+      <c r="I120" s="112"/>
+      <c r="J120" s="112"/>
+      <c r="K120" s="112"/>
+      <c r="L120" s="112"/>
+      <c r="M120" s="113"/>
+    </row>
+    <row r="121" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="114"/>
+      <c r="B121" s="115"/>
+      <c r="C121" s="115"/>
+      <c r="D121" s="115"/>
+      <c r="E121" s="115"/>
+      <c r="F121" s="115"/>
+      <c r="G121" s="115"/>
+      <c r="H121" s="115"/>
+      <c r="I121" s="115"/>
+      <c r="J121" s="115"/>
+      <c r="K121" s="115"/>
+      <c r="L121" s="115"/>
+      <c r="M121" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="C103:H103"/>
+    <mergeCell ref="C76:H76"/>
+    <mergeCell ref="C77:H77"/>
+    <mergeCell ref="C81:H81"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C99:H99"/>
+    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="C116:G116"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A11:M11"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C36:H36"/>
+    <mergeCell ref="C37:H37"/>
+    <mergeCell ref="C41:H41"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I45:J45"/>
     <mergeCell ref="A119:M121"/>
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="C3:C4"/>
@@ -4073,35 +4086,6 @@
     <mergeCell ref="C53:H53"/>
     <mergeCell ref="C57:H57"/>
     <mergeCell ref="I107:J107"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="C116:G116"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="C19:H19"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="C41:H41"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="C103:H103"/>
-    <mergeCell ref="C76:H76"/>
-    <mergeCell ref="C77:H77"/>
-    <mergeCell ref="C81:H81"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C99:H99"/>
-    <mergeCell ref="C72:G72"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026/URIARTE 630/Julio/EXPENSAS-Julio.xlsx
+++ b/2026/URIARTE 630/Julio/EXPENSAS-Julio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\URIARTE 630\Julio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F507839-B6EF-452E-A919-868494FFF957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{182E8EA2-7621-46E5-B861-B6410DF4D07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="detalle y gastos" sheetId="3" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="72">
   <si>
     <t>UF</t>
   </si>
@@ -182,9 +182,6 @@
     <t>FEDERACION PATRONAL POLIZA DE SEGURO OBLIGATORIA</t>
   </si>
   <si>
-    <t>LUCA BASUALDO</t>
-  </si>
-  <si>
     <t xml:space="preserve">VARLAS GUILLERMO </t>
   </si>
   <si>
@@ -233,12 +230,6 @@
     <t>Subidos en JUN10 2026</t>
   </si>
   <si>
-    <t>PREVISION TSG</t>
-  </si>
-  <si>
-    <t>Prevision TSG</t>
-  </si>
-  <si>
     <t>SE DEBEN 5 CUOTAS DE TSG</t>
   </si>
   <si>
@@ -249,6 +240,12 @@
   </si>
   <si>
     <t>Liquidacion mes de JULIO</t>
+  </si>
+  <si>
+    <t>MICAELA YAÑEZ</t>
+  </si>
+  <si>
+    <t>EDESUR</t>
   </si>
 </sst>
 </file>
@@ -1253,63 +1250,29 @@
     <xf numFmtId="164" fontId="10" fillId="6" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1317,11 +1280,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1346,19 +1311,51 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="55" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="6" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="47" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1804,10 +1801,10 @@
       <c r="C7" s="35"/>
       <c r="D7" s="35"/>
       <c r="E7" s="17" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F7" s="45" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1830,17 +1827,17 @@
       <c r="B11" s="19"/>
       <c r="C11" s="20"/>
       <c r="D11" s="4"/>
-      <c r="E11" s="106" t="s">
+      <c r="E11" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="107"/>
+      <c r="F11" s="110"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="93"/>
-      <c r="C12" s="145">
+      <c r="C12" s="108">
         <f>182740/2</f>
         <v>91370</v>
       </c>
@@ -1857,12 +1854,12 @@
         <v>32</v>
       </c>
       <c r="B13" s="93"/>
-      <c r="C13" s="145">
+      <c r="C13" s="108">
         <v>5842.51</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="87" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F13" s="88">
         <f>'prorrateo '!F10</f>
@@ -1879,7 +1876,7 @@
       </c>
       <c r="D14" s="24"/>
       <c r="E14" s="87" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F14" s="97">
         <f>-C23</f>
@@ -1888,7 +1885,7 @@
     </row>
     <row r="15" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="46" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B15" s="93"/>
       <c r="C15" s="100">
@@ -1896,7 +1893,7 @@
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="87" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F15" s="98">
         <v>-222358.64</v>
@@ -1907,23 +1904,23 @@
         <v>30</v>
       </c>
       <c r="B16" s="93"/>
-      <c r="C16" s="145">
+      <c r="C16" s="108">
         <v>79600</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="87" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F16" s="102">
         <v>0</v>
       </c>
       <c r="G16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="143"/>
-      <c r="B17" s="144"/>
+      <c r="A17" s="106"/>
+      <c r="B17" s="107"/>
       <c r="C17" s="105"/>
       <c r="D17" s="4"/>
       <c r="E17" s="87" t="s">
@@ -1935,7 +1932,7 @@
     </row>
     <row r="18" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B18" s="94"/>
       <c r="C18" s="89">
@@ -1963,7 +1960,7 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="93"/>
       <c r="C20" s="100">
@@ -1973,7 +1970,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="64" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21" s="101"/>
       <c r="C21" s="103">
@@ -1983,7 +1980,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="38">
@@ -2031,7 +2028,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C27" s="69"/>
       <c r="F27" s="5"/>
@@ -2152,29 +2149,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="138" t="str">
+      <c r="A1" s="128" t="str">
         <f>'detalle y gastos'!E7</f>
         <v>Liquidacion mes de JULIO</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
       <c r="D1" s="74"/>
       <c r="E1" s="75" t="s">
         <v>25</v>
       </c>
       <c r="F1" s="74"/>
-      <c r="G1" s="133" t="s">
+      <c r="G1" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="134"/>
-      <c r="I1" s="134"/>
-      <c r="J1" s="135"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="125"/>
       <c r="K1" s="91"/>
-      <c r="L1" s="136">
+      <c r="L1" s="126">
         <f>O1</f>
         <v>362147.93000000005</v>
       </c>
-      <c r="M1" s="137"/>
+      <c r="M1" s="127"/>
       <c r="O1" s="14">
         <v>362147.93000000005</v>
       </c>
@@ -2191,72 +2188,76 @@
       <c r="E2" s="40"/>
       <c r="F2" s="41"/>
       <c r="G2" s="40" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H2" s="41"/>
       <c r="I2" s="41"/>
       <c r="J2" s="66"/>
       <c r="K2" s="66"/>
-      <c r="L2" s="141">
-        <v>0</v>
-      </c>
-      <c r="M2" s="142"/>
+      <c r="L2" s="111">
+        <f>-O2</f>
+        <v>222358.64</v>
+      </c>
+      <c r="M2" s="112"/>
+      <c r="O2" s="14">
+        <v>-222358.64</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A3" s="119" t="s">
+      <c r="A3" s="142" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="117" t="s">
+      <c r="C3" s="140" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="117" t="s">
+      <c r="E3" s="140" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="117" t="s">
+      <c r="F3" s="140" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="117" t="s">
+      <c r="G3" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="117" t="s">
+      <c r="H3" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="121" t="s">
+      <c r="I3" s="144" t="s">
+        <v>56</v>
+      </c>
+      <c r="J3" s="144" t="s">
+        <v>71</v>
+      </c>
+      <c r="K3" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="121" t="s">
-        <v>68</v>
-      </c>
-      <c r="K3" s="117" t="s">
-        <v>58</v>
-      </c>
       <c r="L3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="M3" s="78" t="s">
-        <v>53</v>
-      </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="120"/>
+      <c r="A4" s="143"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="118"/>
+      <c r="C4" s="141"/>
       <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="118"/>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="122"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="118"/>
+      <c r="E4" s="141"/>
+      <c r="F4" s="141"/>
+      <c r="G4" s="141"/>
+      <c r="H4" s="141"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="145"/>
+      <c r="K4" s="141"/>
       <c r="L4" s="71" t="str">
         <f>A2</f>
         <v>Vto. 17/08</v>
@@ -2266,7 +2267,7 @@
         <v>Vto 19/07</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2277,7 +2278,7 @@
         <v>0.21</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D5" s="43">
         <v>0.5</v>
@@ -2302,17 +2303,17 @@
         <v>76051.065300000002</v>
       </c>
       <c r="J5" s="9">
-        <f>J$2*D5</f>
-        <v>0</v>
+        <f>L$2*B5</f>
+        <v>46695.314400000003</v>
       </c>
       <c r="K5" s="9"/>
       <c r="L5" s="9">
         <f t="shared" ref="L5:L9" si="0">I5+J5+H5+G5+K5</f>
-        <v>75877.183900000004</v>
+        <v>122572.49830000001</v>
       </c>
       <c r="M5" s="79">
         <f>L5+L5*4%</f>
-        <v>78912.271256000007</v>
+        <v>127475.39823200001</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -2348,16 +2349,16 @@
       </c>
       <c r="J6" s="9">
         <f>L$2*B6</f>
-        <v>0</v>
+        <v>35577.382400000002</v>
       </c>
       <c r="K6" s="9"/>
       <c r="L6" s="9">
         <f t="shared" si="0"/>
-        <v>826107.0576360937</v>
+        <v>861684.44003609382</v>
       </c>
       <c r="M6" s="79">
         <f t="shared" ref="M6:M9" si="3">L6+L6*4%</f>
-        <v>859151.33994153747</v>
+        <v>896151.81763753761</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -2368,7 +2369,7 @@
         <v>0.21</v>
       </c>
       <c r="C7" s="47" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D7" s="43"/>
       <c r="E7" s="99">
@@ -2391,7 +2392,6 @@
         <v>76051.065300000002</v>
       </c>
       <c r="J7" s="9">
-        <f t="shared" ref="J7:J9" si="4">L$2*B7</f>
         <v>0</v>
       </c>
       <c r="K7" s="95"/>
@@ -2435,17 +2435,17 @@
         <v>76051.065300000002</v>
       </c>
       <c r="J8" s="9">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" ref="J7:J9" si="4">L$2*B8</f>
+        <v>46695.314400000003</v>
       </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9">
         <f t="shared" si="0"/>
-        <v>76051.065300000002</v>
+        <v>122746.3797</v>
       </c>
       <c r="M8" s="79">
         <f t="shared" si="3"/>
-        <v>79093.107912000007</v>
+        <v>127656.23488800001</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -2456,7 +2456,7 @@
         <v>0.21</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D9" s="43"/>
       <c r="E9" s="99">
@@ -2480,16 +2480,16 @@
       </c>
       <c r="J9" s="9">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>46695.314400000003</v>
       </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9">
         <f t="shared" si="0"/>
-        <v>76051.065300000002</v>
+        <v>122746.3797</v>
       </c>
       <c r="M9" s="79">
         <f t="shared" si="3"/>
-        <v>79093.107912000007</v>
+        <v>127656.23488800001</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2527,60 +2527,60 @@
       </c>
       <c r="J10" s="85">
         <f>SUM(J5:J9)</f>
-        <v>0</v>
+        <v>175663.32560000001</v>
       </c>
       <c r="K10" s="85"/>
       <c r="L10" s="84">
         <f>SUM(L5:L9)</f>
-        <v>1200853.6338371853</v>
+        <v>1376516.9594371857</v>
       </c>
       <c r="M10" s="86">
         <f>SUM(M5:M9)</f>
-        <v>1248887.7791906733</v>
+        <v>1431577.6378146731</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="55.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="140"/>
-      <c r="B11" s="140"/>
-      <c r="C11" s="140"/>
-      <c r="D11" s="140"/>
-      <c r="E11" s="140"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="140"/>
-      <c r="H11" s="140"/>
-      <c r="I11" s="140"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="140"/>
-      <c r="L11" s="140"/>
-      <c r="M11" s="140"/>
+      <c r="A11" s="130"/>
+      <c r="B11" s="130"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="130"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="130"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="130"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="130"/>
+      <c r="M11" s="130"/>
     </row>
     <row r="12" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M12" s="5"/>
     </row>
     <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="127" t="s">
+      <c r="C14" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="128"/>
-      <c r="H14" s="128"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="116"/>
+      <c r="H14" s="116"/>
       <c r="I14" s="48"/>
       <c r="J14" s="49"/>
       <c r="K14" s="53"/>
       <c r="L14" s="53"/>
     </row>
     <row r="15" spans="1:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="129" t="s">
+      <c r="C15" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="128"/>
-      <c r="E15" s="128"/>
-      <c r="F15" s="128"/>
-      <c r="G15" s="128"/>
-      <c r="H15" s="128"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="116"/>
       <c r="I15" s="50"/>
       <c r="J15" s="51"/>
       <c r="K15" s="53"/>
@@ -2653,14 +2653,14 @@
       </c>
     </row>
     <row r="19" spans="3:20" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="130" t="s">
+      <c r="C19" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="D19" s="131"/>
-      <c r="E19" s="131"/>
-      <c r="F19" s="131"/>
-      <c r="G19" s="131"/>
-      <c r="H19" s="131"/>
+      <c r="D19" s="114"/>
+      <c r="E19" s="114"/>
+      <c r="F19" s="114"/>
+      <c r="G19" s="114"/>
+      <c r="H19" s="114"/>
       <c r="I19" s="50"/>
       <c r="J19" s="51"/>
       <c r="K19" s="53"/>
@@ -2691,17 +2691,17 @@
       <c r="D21" s="53"/>
       <c r="E21" s="53" t="str">
         <f>C5</f>
-        <v>SR PROPIETARIO</v>
+        <v>MICAELA YAÑEZ</v>
       </c>
       <c r="F21" s="53"/>
       <c r="G21" s="53" t="s">
         <v>39</v>
       </c>
       <c r="H21" s="56"/>
-      <c r="I21" s="125" t="s">
+      <c r="I21" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="J21" s="126"/>
+      <c r="J21" s="119"/>
       <c r="K21" s="65"/>
       <c r="L21" s="65"/>
     </row>
@@ -2731,8 +2731,8 @@
       <c r="F23" s="53"/>
       <c r="G23" s="53"/>
       <c r="H23" s="53"/>
-      <c r="I23" s="132"/>
-      <c r="J23" s="126"/>
+      <c r="I23" s="120"/>
+      <c r="J23" s="119"/>
       <c r="K23" s="65"/>
       <c r="L23" s="65"/>
     </row>
@@ -2862,13 +2862,13 @@
       <c r="L31" s="53"/>
     </row>
     <row r="32" spans="3:20" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="123" t="s">
+      <c r="C32" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="D32" s="124"/>
-      <c r="E32" s="124"/>
-      <c r="F32" s="124"/>
-      <c r="G32" s="124"/>
+      <c r="D32" s="122"/>
+      <c r="E32" s="122"/>
+      <c r="F32" s="122"/>
+      <c r="G32" s="122"/>
       <c r="H32" s="92">
         <f>SUM(H24:H31)</f>
         <v>117795.96850000002</v>
@@ -2882,28 +2882,28 @@
     <row r="34" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="35" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="36" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C36" s="127" t="s">
+      <c r="C36" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="128"/>
-      <c r="E36" s="128"/>
-      <c r="F36" s="128"/>
-      <c r="G36" s="128"/>
-      <c r="H36" s="128"/>
+      <c r="D36" s="116"/>
+      <c r="E36" s="116"/>
+      <c r="F36" s="116"/>
+      <c r="G36" s="116"/>
+      <c r="H36" s="116"/>
       <c r="I36" s="48"/>
       <c r="J36" s="49"/>
       <c r="K36" s="53"/>
       <c r="L36" s="53"/>
     </row>
     <row r="37" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="129" t="s">
+      <c r="C37" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="128"/>
-      <c r="E37" s="128"/>
-      <c r="F37" s="128"/>
-      <c r="G37" s="128"/>
-      <c r="H37" s="128"/>
+      <c r="D37" s="116"/>
+      <c r="E37" s="116"/>
+      <c r="F37" s="116"/>
+      <c r="G37" s="116"/>
+      <c r="H37" s="116"/>
       <c r="I37" s="50"/>
       <c r="J37" s="51"/>
       <c r="K37" s="53"/>
@@ -2953,14 +2953,14 @@
       <c r="L40" s="53"/>
     </row>
     <row r="41" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C41" s="130" t="s">
+      <c r="C41" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="131"/>
-      <c r="E41" s="131"/>
-      <c r="F41" s="131"/>
-      <c r="G41" s="131"/>
-      <c r="H41" s="131"/>
+      <c r="D41" s="114"/>
+      <c r="E41" s="114"/>
+      <c r="F41" s="114"/>
+      <c r="G41" s="114"/>
+      <c r="H41" s="114"/>
       <c r="I41" s="50"/>
       <c r="J41" s="51"/>
       <c r="K41" s="53"/>
@@ -2985,17 +2985,17 @@
       <c r="D43" s="53"/>
       <c r="E43" s="53" t="str">
         <f>C7</f>
-        <v>LUCA BASUALDO</v>
+        <v>SR PROPIETARIO</v>
       </c>
       <c r="F43" s="53"/>
       <c r="G43" s="53" t="s">
         <v>39</v>
       </c>
       <c r="H43" s="56"/>
-      <c r="I43" s="125" t="s">
+      <c r="I43" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="J43" s="126"/>
+      <c r="J43" s="119"/>
       <c r="K43" s="65"/>
       <c r="L43" s="65"/>
     </row>
@@ -3025,8 +3025,8 @@
       <c r="F45" s="53"/>
       <c r="G45" s="53"/>
       <c r="H45" s="53"/>
-      <c r="I45" s="132"/>
-      <c r="J45" s="126"/>
+      <c r="I45" s="120"/>
+      <c r="J45" s="119"/>
       <c r="K45" s="65"/>
       <c r="L45" s="65"/>
     </row>
@@ -3072,16 +3072,16 @@
       <c r="L48" s="53"/>
     </row>
     <row r="49" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C49" s="123" t="s">
+      <c r="C49" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="D49" s="124"/>
-      <c r="E49" s="124"/>
-      <c r="F49" s="124"/>
-      <c r="G49" s="124"/>
+      <c r="D49" s="122"/>
+      <c r="E49" s="122"/>
+      <c r="F49" s="122"/>
+      <c r="G49" s="122"/>
       <c r="H49" s="92">
         <f>M6</f>
-        <v>859151.33994153747</v>
+        <v>896151.81763753761</v>
       </c>
       <c r="I49" s="60"/>
       <c r="J49" s="61"/>
@@ -3091,28 +3091,28 @@
     <row r="50" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="52" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C52" s="127" t="s">
+      <c r="C52" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="D52" s="128"/>
-      <c r="E52" s="128"/>
-      <c r="F52" s="128"/>
-      <c r="G52" s="128"/>
-      <c r="H52" s="128"/>
+      <c r="D52" s="116"/>
+      <c r="E52" s="116"/>
+      <c r="F52" s="116"/>
+      <c r="G52" s="116"/>
+      <c r="H52" s="116"/>
       <c r="I52" s="48"/>
       <c r="J52" s="49"/>
       <c r="K52" s="53"/>
       <c r="L52" s="53"/>
     </row>
     <row r="53" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C53" s="129" t="s">
+      <c r="C53" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="D53" s="128"/>
-      <c r="E53" s="128"/>
-      <c r="F53" s="128"/>
-      <c r="G53" s="128"/>
-      <c r="H53" s="128"/>
+      <c r="D53" s="116"/>
+      <c r="E53" s="116"/>
+      <c r="F53" s="116"/>
+      <c r="G53" s="116"/>
+      <c r="H53" s="116"/>
       <c r="I53" s="50"/>
       <c r="J53" s="51"/>
       <c r="K53" s="53"/>
@@ -3162,14 +3162,14 @@
       <c r="L56" s="53"/>
     </row>
     <row r="57" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C57" s="130" t="s">
+      <c r="C57" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="D57" s="131"/>
-      <c r="E57" s="131"/>
-      <c r="F57" s="131"/>
-      <c r="G57" s="131"/>
-      <c r="H57" s="131"/>
+      <c r="D57" s="114"/>
+      <c r="E57" s="114"/>
+      <c r="F57" s="114"/>
+      <c r="G57" s="114"/>
+      <c r="H57" s="114"/>
       <c r="I57" s="50"/>
       <c r="J57" s="51"/>
       <c r="K57" s="53"/>
@@ -3201,10 +3201,10 @@
         <v>39</v>
       </c>
       <c r="H59" s="56"/>
-      <c r="I59" s="125" t="s">
+      <c r="I59" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="J59" s="126"/>
+      <c r="J59" s="119"/>
       <c r="K59" s="65"/>
       <c r="L59" s="65"/>
     </row>
@@ -3234,8 +3234,8 @@
       <c r="F61" s="53"/>
       <c r="G61" s="53"/>
       <c r="H61" s="53"/>
-      <c r="I61" s="132"/>
-      <c r="J61" s="126"/>
+      <c r="I61" s="120"/>
+      <c r="J61" s="119"/>
       <c r="K61" s="65"/>
       <c r="L61" s="65"/>
     </row>
@@ -3389,13 +3389,13 @@
       <c r="L71" s="53"/>
     </row>
     <row r="72" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C72" s="123" t="s">
+      <c r="C72" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="D72" s="124"/>
-      <c r="E72" s="124"/>
-      <c r="F72" s="124"/>
-      <c r="G72" s="124"/>
+      <c r="D72" s="122"/>
+      <c r="E72" s="122"/>
+      <c r="F72" s="122"/>
+      <c r="G72" s="122"/>
       <c r="H72" s="92">
         <f>SUM(H62:H71)</f>
         <v>117795.96850000002</v>
@@ -3409,28 +3409,28 @@
     <row r="74" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="75" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="76" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C76" s="127" t="s">
+      <c r="C76" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="D76" s="128"/>
-      <c r="E76" s="128"/>
-      <c r="F76" s="128"/>
-      <c r="G76" s="128"/>
-      <c r="H76" s="128"/>
+      <c r="D76" s="116"/>
+      <c r="E76" s="116"/>
+      <c r="F76" s="116"/>
+      <c r="G76" s="116"/>
+      <c r="H76" s="116"/>
       <c r="I76" s="48"/>
       <c r="J76" s="49"/>
       <c r="K76" s="53"/>
       <c r="L76" s="53"/>
     </row>
     <row r="77" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="129" t="s">
+      <c r="C77" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="D77" s="128"/>
-      <c r="E77" s="128"/>
-      <c r="F77" s="128"/>
-      <c r="G77" s="128"/>
-      <c r="H77" s="128"/>
+      <c r="D77" s="116"/>
+      <c r="E77" s="116"/>
+      <c r="F77" s="116"/>
+      <c r="G77" s="116"/>
+      <c r="H77" s="116"/>
       <c r="I77" s="50"/>
       <c r="J77" s="51"/>
       <c r="K77" s="53"/>
@@ -3480,14 +3480,14 @@
       <c r="L80" s="53"/>
     </row>
     <row r="81" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C81" s="130" t="s">
+      <c r="C81" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="D81" s="131"/>
-      <c r="E81" s="131"/>
-      <c r="F81" s="131"/>
-      <c r="G81" s="131"/>
-      <c r="H81" s="131"/>
+      <c r="D81" s="114"/>
+      <c r="E81" s="114"/>
+      <c r="F81" s="114"/>
+      <c r="G81" s="114"/>
+      <c r="H81" s="114"/>
       <c r="I81" s="50"/>
       <c r="J81" s="51"/>
       <c r="K81" s="53"/>
@@ -3519,10 +3519,10 @@
         <v>39</v>
       </c>
       <c r="H83" s="56"/>
-      <c r="I83" s="125" t="s">
+      <c r="I83" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="J83" s="126"/>
+      <c r="J83" s="119"/>
       <c r="K83" s="65"/>
       <c r="L83" s="65"/>
     </row>
@@ -3552,8 +3552,8 @@
       <c r="F85" s="53"/>
       <c r="G85" s="53"/>
       <c r="H85" s="53"/>
-      <c r="I85" s="132"/>
-      <c r="J85" s="126"/>
+      <c r="I85" s="120"/>
+      <c r="J85" s="119"/>
       <c r="K85" s="65"/>
       <c r="L85" s="65"/>
     </row>
@@ -3682,13 +3682,13 @@
       <c r="L93" s="53"/>
     </row>
     <row r="94" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C94" s="123" t="s">
+      <c r="C94" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="D94" s="124"/>
-      <c r="E94" s="124"/>
-      <c r="F94" s="124"/>
-      <c r="G94" s="124"/>
+      <c r="D94" s="122"/>
+      <c r="E94" s="122"/>
+      <c r="F94" s="122"/>
+      <c r="G94" s="122"/>
       <c r="H94" s="92">
         <f>SUM(H86:H93)</f>
         <v>117795.96850000002</v>
@@ -3702,28 +3702,28 @@
     <row r="96" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="97" spans="3:12" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="98" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C98" s="127" t="s">
+      <c r="C98" s="115" t="s">
         <v>34</v>
       </c>
-      <c r="D98" s="128"/>
-      <c r="E98" s="128"/>
-      <c r="F98" s="128"/>
-      <c r="G98" s="128"/>
-      <c r="H98" s="128"/>
+      <c r="D98" s="116"/>
+      <c r="E98" s="116"/>
+      <c r="F98" s="116"/>
+      <c r="G98" s="116"/>
+      <c r="H98" s="116"/>
       <c r="I98" s="48"/>
       <c r="J98" s="49"/>
       <c r="K98" s="53"/>
       <c r="L98" s="53"/>
     </row>
     <row r="99" spans="3:12" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C99" s="129" t="s">
+      <c r="C99" s="117" t="s">
         <v>35</v>
       </c>
-      <c r="D99" s="128"/>
-      <c r="E99" s="128"/>
-      <c r="F99" s="128"/>
-      <c r="G99" s="128"/>
-      <c r="H99" s="128"/>
+      <c r="D99" s="116"/>
+      <c r="E99" s="116"/>
+      <c r="F99" s="116"/>
+      <c r="G99" s="116"/>
+      <c r="H99" s="116"/>
       <c r="I99" s="50"/>
       <c r="J99" s="51"/>
       <c r="K99" s="53"/>
@@ -3773,14 +3773,14 @@
       <c r="L102" s="53"/>
     </row>
     <row r="103" spans="3:12" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C103" s="130" t="s">
+      <c r="C103" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="D103" s="131"/>
-      <c r="E103" s="131"/>
-      <c r="F103" s="131"/>
-      <c r="G103" s="131"/>
-      <c r="H103" s="131"/>
+      <c r="D103" s="114"/>
+      <c r="E103" s="114"/>
+      <c r="F103" s="114"/>
+      <c r="G103" s="114"/>
+      <c r="H103" s="114"/>
       <c r="I103" s="50"/>
       <c r="J103" s="51"/>
       <c r="K103" s="53"/>
@@ -3812,10 +3812,10 @@
         <v>39</v>
       </c>
       <c r="H105" s="56"/>
-      <c r="I105" s="125" t="s">
+      <c r="I105" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="J105" s="126"/>
+      <c r="J105" s="119"/>
       <c r="K105" s="65"/>
       <c r="L105" s="65"/>
     </row>
@@ -3844,8 +3844,8 @@
       <c r="F107" s="53"/>
       <c r="G107" s="53"/>
       <c r="H107" s="53"/>
-      <c r="I107" s="132"/>
-      <c r="J107" s="126"/>
+      <c r="I107" s="120"/>
+      <c r="J107" s="119"/>
       <c r="K107" s="65"/>
       <c r="L107" s="65"/>
     </row>
@@ -3974,13 +3974,13 @@
       <c r="L115" s="53"/>
     </row>
     <row r="116" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C116" s="123" t="s">
+      <c r="C116" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="D116" s="124"/>
-      <c r="E116" s="124"/>
-      <c r="F116" s="124"/>
-      <c r="G116" s="124"/>
+      <c r="D116" s="122"/>
+      <c r="E116" s="122"/>
+      <c r="F116" s="122"/>
+      <c r="G116" s="122"/>
       <c r="H116" s="92">
         <f>SUM(H108:H115)</f>
         <v>117795.96850000002</v>
@@ -3993,67 +3993,70 @@
     <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="108" t="s">
-        <v>69</v>
-      </c>
-      <c r="B119" s="109"/>
-      <c r="C119" s="109"/>
-      <c r="D119" s="109"/>
-      <c r="E119" s="109"/>
-      <c r="F119" s="109"/>
-      <c r="G119" s="109"/>
-      <c r="H119" s="109"/>
-      <c r="I119" s="109"/>
-      <c r="J119" s="109"/>
-      <c r="K119" s="109"/>
-      <c r="L119" s="109"/>
-      <c r="M119" s="110"/>
+      <c r="A119" s="131" t="s">
+        <v>66</v>
+      </c>
+      <c r="B119" s="132"/>
+      <c r="C119" s="132"/>
+      <c r="D119" s="132"/>
+      <c r="E119" s="132"/>
+      <c r="F119" s="132"/>
+      <c r="G119" s="132"/>
+      <c r="H119" s="132"/>
+      <c r="I119" s="132"/>
+      <c r="J119" s="132"/>
+      <c r="K119" s="132"/>
+      <c r="L119" s="132"/>
+      <c r="M119" s="133"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="111"/>
-      <c r="B120" s="112"/>
-      <c r="C120" s="112"/>
-      <c r="D120" s="112"/>
-      <c r="E120" s="112"/>
-      <c r="F120" s="112"/>
-      <c r="G120" s="112"/>
-      <c r="H120" s="112"/>
-      <c r="I120" s="112"/>
-      <c r="J120" s="112"/>
-      <c r="K120" s="112"/>
-      <c r="L120" s="112"/>
-      <c r="M120" s="113"/>
+      <c r="A120" s="134"/>
+      <c r="B120" s="135"/>
+      <c r="C120" s="135"/>
+      <c r="D120" s="135"/>
+      <c r="E120" s="135"/>
+      <c r="F120" s="135"/>
+      <c r="G120" s="135"/>
+      <c r="H120" s="135"/>
+      <c r="I120" s="135"/>
+      <c r="J120" s="135"/>
+      <c r="K120" s="135"/>
+      <c r="L120" s="135"/>
+      <c r="M120" s="136"/>
     </row>
     <row r="121" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="114"/>
-      <c r="B121" s="115"/>
-      <c r="C121" s="115"/>
-      <c r="D121" s="115"/>
-      <c r="E121" s="115"/>
-      <c r="F121" s="115"/>
-      <c r="G121" s="115"/>
-      <c r="H121" s="115"/>
-      <c r="I121" s="115"/>
-      <c r="J121" s="115"/>
-      <c r="K121" s="115"/>
-      <c r="L121" s="115"/>
-      <c r="M121" s="116"/>
+      <c r="A121" s="137"/>
+      <c r="B121" s="138"/>
+      <c r="C121" s="138"/>
+      <c r="D121" s="138"/>
+      <c r="E121" s="138"/>
+      <c r="F121" s="138"/>
+      <c r="G121" s="138"/>
+      <c r="H121" s="138"/>
+      <c r="I121" s="138"/>
+      <c r="J121" s="138"/>
+      <c r="K121" s="138"/>
+      <c r="L121" s="138"/>
+      <c r="M121" s="139"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="C103:H103"/>
-    <mergeCell ref="C76:H76"/>
-    <mergeCell ref="C77:H77"/>
-    <mergeCell ref="C81:H81"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="C94:G94"/>
-    <mergeCell ref="I59:J59"/>
-    <mergeCell ref="I61:J61"/>
-    <mergeCell ref="C98:H98"/>
-    <mergeCell ref="C99:H99"/>
-    <mergeCell ref="C72:G72"/>
+    <mergeCell ref="A119:M121"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="I105:J105"/>
+    <mergeCell ref="C52:H52"/>
+    <mergeCell ref="C53:H53"/>
+    <mergeCell ref="C57:H57"/>
+    <mergeCell ref="I107:J107"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="C116:G116"/>
@@ -4070,22 +4073,19 @@
     <mergeCell ref="C41:H41"/>
     <mergeCell ref="I43:J43"/>
     <mergeCell ref="I45:J45"/>
-    <mergeCell ref="A119:M121"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="C49:G49"/>
-    <mergeCell ref="I105:J105"/>
-    <mergeCell ref="C52:H52"/>
-    <mergeCell ref="C53:H53"/>
-    <mergeCell ref="C57:H57"/>
-    <mergeCell ref="I107:J107"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="C103:H103"/>
+    <mergeCell ref="C76:H76"/>
+    <mergeCell ref="C77:H77"/>
+    <mergeCell ref="C81:H81"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="C94:G94"/>
+    <mergeCell ref="I59:J59"/>
+    <mergeCell ref="I61:J61"/>
+    <mergeCell ref="C98:H98"/>
+    <mergeCell ref="C99:H99"/>
+    <mergeCell ref="C72:G72"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
